--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -1367,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AV11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="14"/>
@@ -1398,9 +1398,26 @@
     <col customWidth="1" max="26" min="26" width="14"/>
     <col customWidth="1" max="27" min="27" width="14"/>
     <col customWidth="1" max="28" min="28" width="14"/>
-    <col customWidth="1" hidden="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
     <col customWidth="1" max="30" min="30" width="14"/>
     <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" hidden="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1566,30 +1583,115 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>Simple gates met (Stage 2)</t>
+          <t>Simple gates met</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
           <t>Num. Sessions</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
         <is>
           <t>Session started</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>Session data (local path)</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
         <is>
           <t>Session struct (local path)</t>
         </is>
@@ -1631,6 +1733,23 @@
       <c r="AC8" s="11" t="n"/>
       <c r="AD8" s="11" t="n"/>
       <c r="AE8" s="11" t="n"/>
+      <c r="AF8" s="11" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+      <c r="AH8" s="11" t="n"/>
+      <c r="AI8" s="11" t="n"/>
+      <c r="AJ8" s="11" t="n"/>
+      <c r="AK8" s="11" t="n"/>
+      <c r="AL8" s="11" t="n"/>
+      <c r="AM8" s="11" t="n"/>
+      <c r="AN8" s="11" t="n"/>
+      <c r="AO8" s="11" t="n"/>
+      <c r="AP8" s="11" t="n"/>
+      <c r="AQ8" s="11" t="n"/>
+      <c r="AR8" s="11" t="n"/>
+      <c r="AS8" s="11" t="n"/>
+      <c r="AT8" s="11" t="n"/>
+      <c r="AU8" s="11" t="n"/>
+      <c r="AV8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1684,20 +1803,44 @@
       <c r="W9" t="n">
         <v>0.09999999999999964</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AG9" s="4" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
         <v>2</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>2026-08-26 12:13:37.010861; 2026-08-26 12:16:13.061661</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121335\20260826-121335.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121612\20260826-121612.csv</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121335\20260826-121335_combined_struct.mat</t>
         </is>
@@ -1755,12 +1898,36 @@
       <c r="W10" t="n">
         <v>0.09999999999999964</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AG10" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr">
         <is>
           <t>2026-09-03 12:27:24.305170</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260903-122723\20260903-122723.csv</t>
         </is>
@@ -1818,20 +1985,44 @@
       <c r="W11" t="n">
         <v>0.09999999999999964</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AG11" s="4" t="n">
+        <v>0.5188419117647058</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
         <v>2</v>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>2026-09-04 11:00:25.643470; 2026-09-04 11:02:49.857724</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110248\20260904-110248.csv</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024_combined_struct.mat</t>
         </is>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="test" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="testTask" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="test_stage1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="test_stage2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="test_stage3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +43,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +65,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +98,8 @@
     <xf borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
@@ -1367,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV11"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="14"/>
@@ -1415,9 +1425,12 @@
     <col customWidth="1" max="43" min="43" width="14"/>
     <col customWidth="1" max="44" min="44" width="14"/>
     <col customWidth="1" max="45" min="45" width="14"/>
-    <col customWidth="1" hidden="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
     <col customWidth="1" max="47" min="47" width="14"/>
     <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1673,25 +1686,40 @@
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
           <t>Num. Sessions</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>Session started</t>
         </is>
       </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Session data (local path)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
+      <c r="AY7" s="3" t="inlineStr">
         <is>
           <t>Session struct (local path)</t>
         </is>
@@ -1750,6 +1778,9 @@
       <c r="AT8" s="11" t="n"/>
       <c r="AU8" s="11" t="n"/>
       <c r="AV8" s="11" t="n"/>
+      <c r="AW8" s="11" t="n"/>
+      <c r="AX8" s="11" t="n"/>
+      <c r="AY8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1827,20 +1858,20 @@
       <c r="AN9" t="n">
         <v>0</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AU9" t="n">
         <v>2</v>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>2026-08-26 12:13:37.010861; 2026-08-26 12:16:13.061661</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121335\20260826-121335.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121612\20260826-121612.csv</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260826-121335\20260826-121335_combined_struct.mat</t>
         </is>
@@ -1922,12 +1953,12 @@
       <c r="AN10" t="n">
         <v>0</v>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>2026-09-03 12:27:24.305170</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260903-122723\20260903-122723.csv</t>
         </is>
@@ -2009,22 +2040,1783 @@
       <c r="AN11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:00:25.643470; 2026-09-04 11:02:49.857724</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110248\20260904-110248.csv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024_combined_struct.mat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Animal: test_stage1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Weight (g)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Reward Amount (uL)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Total Volume (uL)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Withheld</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No-movement</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>L turns</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R turns</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Licks</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold start (deg)</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (deg)</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (% final)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ITI (s)</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Gain mult (Stage 1)</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Direction ratio (Stage 2)</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Num. Sessions</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>Session started</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Session data (local path)</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>Session struct (local path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="7" t="n"/>
+      <c r="AE8" s="7" t="n"/>
+      <c r="AF8" s="7" t="n"/>
+      <c r="AG8" s="7" t="n"/>
+      <c r="AH8" s="7" t="n"/>
+      <c r="AI8" s="7" t="n"/>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="7" t="n"/>
+      <c r="AS8" s="7" t="n"/>
+      <c r="AT8" s="7" t="n"/>
+      <c r="AU8" s="7" t="n"/>
+      <c r="AV8" s="7" t="n"/>
+      <c r="AW8" s="7" t="n"/>
+      <c r="AX8" s="7" t="n"/>
+      <c r="AY8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="D9" s="5">
+        <f>IFERROR(C9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v>36</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.0867</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>79</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:48:02.576818; 2026-09-18 10:55:13.692823</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-105512\20260918-105512.csv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801_combined_struct.mat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Animal: test_stage2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Weight (g)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Reward Amount (uL)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Total Volume (uL)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Withheld</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No-movement</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>L turns</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R turns</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Licks</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold start (deg)</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (deg)</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (% final)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ITI (s)</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Gain mult (Stage 1)</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Direction ratio (Stage 2)</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Num. Sessions</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>Session started</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Session data (local path)</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>Session struct (local path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="9" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="9" t="n"/>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="9" t="n"/>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="9" t="n"/>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="9" t="n"/>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="9" t="n"/>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="9" t="n"/>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="9" t="n"/>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="9" t="n"/>
+      <c r="AY8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="D9" s="5">
+        <f>IFERROR(C9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v>37</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.3952</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>101</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:57:38.677951</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737.csv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737_struct.mat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Animal: test_stage3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Weight (g)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Reward Amount (uL)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Total Volume (uL)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Withheld</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No-movement</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>L turns</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R turns</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Licks</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold start (deg)</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (deg)</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (% final)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ITI (s)</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Gain mult (Stage 1)</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Direction ratio (Stage 2)</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Num. Sessions</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>Session started</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Session data (local path)</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>Session struct (local path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="13" t="n"/>
+      <c r="AC8" s="13" t="n"/>
+      <c r="AD8" s="13" t="n"/>
+      <c r="AE8" s="13" t="n"/>
+      <c r="AF8" s="13" t="n"/>
+      <c r="AG8" s="13" t="n"/>
+      <c r="AH8" s="13" t="n"/>
+      <c r="AI8" s="13" t="n"/>
+      <c r="AJ8" s="13" t="n"/>
+      <c r="AK8" s="13" t="n"/>
+      <c r="AL8" s="13" t="n"/>
+      <c r="AM8" s="13" t="n"/>
+      <c r="AN8" s="13" t="n"/>
+      <c r="AO8" s="13" t="n"/>
+      <c r="AP8" s="13" t="n"/>
+      <c r="AQ8" s="13" t="n"/>
+      <c r="AR8" s="13" t="n"/>
+      <c r="AS8" s="13" t="n"/>
+      <c r="AT8" s="13" t="n"/>
+      <c r="AU8" s="13" t="n"/>
+      <c r="AV8" s="13" t="n"/>
+      <c r="AW8" s="13" t="n"/>
+      <c r="AX8" s="13" t="n"/>
+      <c r="AY8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="D9" s="5">
+        <f>IFERROR(C9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:07:35.895474</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110734\20260918-110734.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="D10" s="5">
+        <f>IFERROR(C10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>IFERROR(E10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:09:41.608956</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110940\20260918-110940.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="D11" s="5">
+        <f>IFERROR(C11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>IFERROR(E11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v>76</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23.0096</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>30</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>0.06578947368421052</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AR11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>2026-09-04 11:00:25.643470; 2026-09-04 11:02:49.857724</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110248\20260904-110248.csv</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\..\Tests\experiments\Task\setups\Full\sessions\20260904-110024\20260904-110024_combined_struct.mat</t>
+        <v>70</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:43.713222; 2026-09-18 15:37:53.276990; 2026-09-18 16:09:07.462610; 2026-09-18 16:12:06.495495; 2026-09-18 16:38:36.208995</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153752\20260918-153752.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-160906\20260918-160906.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-161205\20260918-161205.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-163835\20260918-163835.csv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642_combined_struct.mat</t>
         </is>
       </c>
     </row>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="14"/>
@@ -2582,6 +2582,321 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801_combined_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="D10" s="5">
+        <f>IFERROR(C10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>IFERROR(E10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.8689</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:02:13.065471; 2026-09-29 12:03:46.520957; 2026-09-29 12:04:34.271655</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120345\20260929-120345.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120433\20260929-120433.csv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212_combined_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="D11" s="5">
+        <f>IFERROR(C11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>IFERROR(E11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.3915</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:27:56.879192</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756.csv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="D12" s="5">
+        <f>IFERROR(C12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>IFERROR(E12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20.8231</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57:42.108067; 2026-09-29 16:16:29.305653; 2026-09-29 16:20:19.853590; 2026-09-29 16:22:43.629419</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-161628\20260929-161628.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162019\20260929-162019.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162242\20260929-162242.csv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741_combined_struct.mat</t>
         </is>
       </c>
     </row>
@@ -3713,34 +4028,40 @@
         <v/>
       </c>
       <c r="H11" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="I11" t="n">
-        <v>23.0096</v>
+        <v>35.70160000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
@@ -3767,25 +4088,25 @@
         <v>0</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>0.06578947368421052</v>
+        <v>0.06504065040650407</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
@@ -3802,16 +4123,16 @@
         <v>10000</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:36:43.713222; 2026-09-18 15:37:53.276990; 2026-09-18 16:09:07.462610; 2026-09-18 16:12:06.495495; 2026-09-18 16:38:36.208995</t>
+          <t>2026-09-18 15:36:43.713222; 2026-09-18 15:37:53.276990; 2026-09-18 16:09:07.462610; 2026-09-18 16:12:06.495495; 2026-09-18 16:38:36.208995; 2026-09-18 17:04:41.641105; 2026-09-18 17:10:06.487381</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153752\20260918-153752.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-160906\20260918-160906.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-161205\20260918-161205.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-163835\20260918-163835.csv</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153752\20260918-153752.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-160906\20260918-160906.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-161205\20260918-161205.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-163835\20260918-163835.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-170440\20260918-170440.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-171005\20260918-171005.csv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -9,9 +9,8 @@
   <sheets>
     <sheet name="test" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="testTask" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="test_stage1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="test_stage2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="test_stage3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="test2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="test3" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="14"/>
@@ -491,12 +490,34 @@
     <col customWidth="1" max="21" min="21" width="14"/>
     <col customWidth="1" max="22" min="22" width="14"/>
     <col customWidth="1" max="23" min="23" width="14"/>
-    <col customWidth="1" hidden="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
     <col customWidth="1" max="25" min="25" width="14"/>
     <col customWidth="1" max="26" min="26" width="14"/>
     <col customWidth="1" max="27" min="27" width="14"/>
     <col customWidth="1" max="28" min="28" width="14"/>
     <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -562,110 +583,235 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>Trials</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Duration (s)</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Reward Amount (uL)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Total Volume (uL)</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Aborts</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Withheld</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>No-movement</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>L turns</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>R turns</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>Licks</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Threshold start (deg)</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>Threshold end (deg)</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Threshold end (% final)</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t>ITI (s)</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>Gain mult (Stage 1)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>Direction ratio (Stage 2)</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>Simple gates met (Stage 2)</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>Num. Sessions</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>Session started</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Session data (local path)</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="AY7" s="3" t="inlineStr">
         <is>
           <t>Session struct (local path)</t>
         </is>
@@ -702,187 +848,273 @@
       <c r="X8" s="7" t="n"/>
       <c r="Y8" s="7" t="n"/>
       <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="7" t="n"/>
+      <c r="AE8" s="7" t="n"/>
+      <c r="AF8" s="7" t="n"/>
+      <c r="AG8" s="7" t="n"/>
+      <c r="AH8" s="7" t="n"/>
+      <c r="AI8" s="7" t="n"/>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="7" t="n"/>
+      <c r="AS8" s="7" t="n"/>
+      <c r="AT8" s="7" t="n"/>
+      <c r="AU8" s="7" t="n"/>
+      <c r="AV8" s="7" t="n"/>
+      <c r="AW8" s="7" t="n"/>
+      <c r="AX8" s="7" t="n"/>
+      <c r="AY8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>22.5</v>
+          <t>10:48</t>
+        </is>
       </c>
       <c r="D9" s="5">
         <f>IFERROR(C9/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E9" t="n">
-        <v>140</v>
-      </c>
-      <c r="F9" t="n">
-        <v>18.6963</v>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v>36</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>11.0867</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>79</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>101</v>
-      </c>
-      <c r="M9" t="n">
-        <v>38</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>handled by hand</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2026-08-11 13:41:46.605630; 2026-08-11 13:46:30.773972</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260811-134145\20260811-134145.csv; C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260811-134630\20260811-134630.csv</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260811-134145\20260811-134145_combined_struct.mat</t>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:48:02.576818; 2026-09-18 10:55:13.692823</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-105512\20260918-105512.csv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801_combined_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="D10" s="5">
         <f>IFERROR(C10/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" s="5">
+        <f>IFERROR(E10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.8689</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" t="n">
-        <v>4.019900000000001</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="T10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2026-08-13 11:14:02.776900</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-111402\20260813-111402.csv</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-111402\20260813-111402_struct.mat</t>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:02:13.065471; 2026-09-29 12:03:46.520957; 2026-09-29 12:04:34.271655</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120345\20260929-120345.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120433\20260929-120433.csv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212_combined_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="D11" s="5">
         <f>IFERROR(C11/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
+      <c r="F11" s="5">
+        <f>IFERROR(E11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>10.3915</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -894,174 +1126,289 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2026-08-13 13:22:19.337954</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-132218\20260813-132218.csv</t>
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:27:56.879192</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756.csv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="D12" s="5">
         <f>IFERROR(C12/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E12" t="n">
-        <v>47</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11.9186</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F12" s="5">
+        <f>IFERROR(E12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I12" t="n">
+        <v>29.1034</v>
+      </c>
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="n">
+        <v>40</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.75</v>
       </c>
-      <c r="P12" t="n">
+      <c r="U12" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="R12" t="n">
+      <c r="W12" t="n">
         <v>0.5</v>
       </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2026-08-13 13:29:35.160305; 2026-08-13 13:31:59.325021</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-132934\20260813-132934.csv; C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-133158\20260813-133158.csv</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260813-132934\20260813-132934_combined_struct.mat</t>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57:42.108067; 2026-09-29 16:16:29.305653; 2026-09-29 16:20:19.853590; 2026-09-29 16:22:43.629419; 2026-09-29 16:33:21.626011</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-161628\20260929-161628.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162019\20260929-162019.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162242\20260929-162242.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-163320\20260929-163320.csv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741_combined_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="D13" s="5">
         <f>IFERROR(C13/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E13" t="n">
-        <v>49</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5.7506</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F13" s="5">
+        <f>IFERROR(E13/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.5183</v>
+      </c>
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.75</v>
       </c>
-      <c r="P13" t="n">
+      <c r="U13" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X13" t="n">
         <v>3</v>
       </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2026-08-17 11:58:22.184887; 2026-08-17 12:08:06.887277</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260817-115818\20260817-115818.csv; C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260817-120806\20260817-120806.csv</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage1\sessions\20260817-115818\20260817-115818_combined_struct.mat</t>
+      <c r="AH13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:39:36.248738</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-143935\20261008-143935.csv</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-143935\20261008-143935_struct.mat</t>
         </is>
       </c>
     </row>
@@ -1096,273 +1443,495 @@
       <c r="X14" s="9" t="n"/>
       <c r="Y14" s="9" t="n"/>
       <c r="Z14" s="9" t="n"/>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="9" t="n"/>
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="9" t="n"/>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="9" t="n"/>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="9" t="n"/>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="9" t="n"/>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="9" t="n"/>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="9" t="n"/>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="9" t="n"/>
+      <c r="AY14" s="9" t="n"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="D15" s="5">
         <f>IFERROR(C15/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
+      <c r="F15" s="5">
+        <f>IFERROR(E15/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v>37</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>10.3952</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260811-135342\20260811-135342.csv</t>
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:57:38.677951</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737.csv</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="D16" s="5">
-        <f>IFERROR(C16/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v>137</v>
-      </c>
-      <c r="F16" t="n">
-        <v>16.8609</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>26</v>
-      </c>
-      <c r="L16" t="n">
-        <v>69</v>
-      </c>
-      <c r="M16" t="n">
-        <v>42</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2026-08-11 13:51:34.028274; 2026-08-11 13:53:54.632954</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260811-135132\20260811-135132.csv; C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260811-135354\20260811-135354.csv</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260811-135132\20260811-135132_combined_struct.mat</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="13" t="n"/>
+      <c r="Z16" s="13" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="13" t="n"/>
+      <c r="AC16" s="13" t="n"/>
+      <c r="AD16" s="13" t="n"/>
+      <c r="AE16" s="13" t="n"/>
+      <c r="AF16" s="13" t="n"/>
+      <c r="AG16" s="13" t="n"/>
+      <c r="AH16" s="13" t="n"/>
+      <c r="AI16" s="13" t="n"/>
+      <c r="AJ16" s="13" t="n"/>
+      <c r="AK16" s="13" t="n"/>
+      <c r="AL16" s="13" t="n"/>
+      <c r="AM16" s="13" t="n"/>
+      <c r="AN16" s="13" t="n"/>
+      <c r="AO16" s="13" t="n"/>
+      <c r="AP16" s="13" t="n"/>
+      <c r="AQ16" s="13" t="n"/>
+      <c r="AR16" s="13" t="n"/>
+      <c r="AS16" s="13" t="n"/>
+      <c r="AT16" s="13" t="n"/>
+      <c r="AU16" s="13" t="n"/>
+      <c r="AV16" s="13" t="n"/>
+      <c r="AW16" s="13" t="n"/>
+      <c r="AX16" s="13" t="n"/>
+      <c r="AY16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="D17" s="5">
         <f>IFERROR(C17/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E17" t="n">
-        <v>33</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.078</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
+      <c r="F17" s="5">
+        <f>IFERROR(E17/$B$5,"")</f>
+        <v/>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2026-08-13 13:41:49.500571</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260813-134148\20260813-134148.csv</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260813-134148\20260813-134148_struct.mat</t>
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:07:35.895474</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110734\20260918-110734.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="D18" s="5">
         <f>IFERROR(C18/$B$5,"")</f>
         <v/>
       </c>
-      <c r="E18" t="n">
-        <v>29</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.306100000000001</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18" s="5">
+        <f>IFERROR(E18/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:09:41.608956</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110940\20260918-110940.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="D19" s="5">
+        <f>IFERROR(C19/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>IFERROR(E19/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v>123</v>
+      </c>
+      <c r="I19" t="n">
+        <v>35.70160000000001</v>
+      </c>
+      <c r="J19" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>20</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5.250000000000001</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2026-08-17 13:21:11.675718; 2026-08-17 13:22:19.871948</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260817-132110\20260817-132110.csv; C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260817-132219\20260817-132219.csv</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>C:\Users\2P-Behav\Documents\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Training\setups\Stage2\sessions\20260817-132110\20260817-132110_combined_struct.mat</t>
+      <c r="K19" t="n">
+        <v>28</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>17</v>
+      </c>
+      <c r="R19" t="n">
+        <v>25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>62</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="4" t="n">
+        <v>0.06504065040650407</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AR19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:36:43.713222; 2026-09-18 15:37:53.276990; 2026-09-18 16:09:07.462610; 2026-09-18 16:12:06.495495; 2026-09-18 16:38:36.208995; 2026-09-18 17:04:41.641105; 2026-09-18 17:10:06.487381</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153752\20260918-153752.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-160906\20260918-160906.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-161205\20260918-161205.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-163835\20260918-163835.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-170440\20260918-170440.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-171005\20260918-171005.csv</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642_combined_struct.mat</t>
         </is>
       </c>
     </row>
@@ -2070,6 +2639,563 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AY9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Animal: test2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>black6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Weight (g)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Reward Amount (uL)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Total Volume (uL)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Withheld</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No-movement</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>L turns</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R turns</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Licks</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold start (deg)</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (deg)</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (% final)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ITI (s)</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Gain mult (Stage 1)</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Direction ratio (Stage 2)</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 3)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Num. Sessions</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>Session started</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Session data (local path)</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>Session struct (local path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="7" t="n"/>
+      <c r="AE8" s="7" t="n"/>
+      <c r="AF8" s="7" t="n"/>
+      <c r="AG8" s="7" t="n"/>
+      <c r="AH8" s="7" t="n"/>
+      <c r="AI8" s="7" t="n"/>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="7" t="n"/>
+      <c r="AS8" s="7" t="n"/>
+      <c r="AT8" s="7" t="n"/>
+      <c r="AU8" s="7" t="n"/>
+      <c r="AV8" s="7" t="n"/>
+      <c r="AW8" s="7" t="n"/>
+      <c r="AX8" s="7" t="n"/>
+      <c r="AY8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <f>IFERROR(C9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.3982</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>blah</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:02:19.553098</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-160218\20261008-160218.csv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-160218\20261008-160218_struct.mat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2129,7 +3255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Animal: test_stage1</t>
+          <t>Animal: test3</t>
         </is>
       </c>
     </row>
@@ -2139,6 +3265,11 @@
           <t>DOB</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2146,6 +3277,11 @@
           <t>Sex</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2153,11 +3289,21 @@
           <t>Strain</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Baseline weight (g)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2478,12 +3624,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="D9" s="5">
@@ -2494,11 +3640,11 @@
         <f>IFERROR(E9/$B$5,"")</f>
         <v/>
       </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
       <c r="H9" t="n">
-        <v>36</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11.0867</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -2522,31 +3668,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>35</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2566,140 +3703,80 @@
       <c r="AN9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="n">
-        <v>2</v>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2026-09-18 10:48:02.576818; 2026-09-18 10:55:13.692823</t>
+          <t>2026-10-08 16:37:07.526170</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-105512\20260918-105512.csv</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-163706\20261008-163706.csv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260918-104801\20260918-104801_combined_struct.mat</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261008-163706\20261008-163706_struct.mat</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="D10" s="5">
-        <f>IFERROR(C10/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>IFERROR(E10/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.8689</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AH10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:02:13.065471; 2026-09-29 12:03:46.520957; 2026-09-29 12:04:34.271655</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120345\20260929-120345.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120433\20260929-120433.csv</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-120212\20260929-120212_combined_struct.mat</t>
-        </is>
-      </c>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="13" t="n"/>
+      <c r="AD10" s="13" t="n"/>
+      <c r="AE10" s="13" t="n"/>
+      <c r="AF10" s="13" t="n"/>
+      <c r="AG10" s="13" t="n"/>
+      <c r="AH10" s="13" t="n"/>
+      <c r="AI10" s="13" t="n"/>
+      <c r="AJ10" s="13" t="n"/>
+      <c r="AK10" s="13" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="13" t="n"/>
+      <c r="AN10" s="13" t="n"/>
+      <c r="AO10" s="13" t="n"/>
+      <c r="AP10" s="13" t="n"/>
+      <c r="AQ10" s="13" t="n"/>
+      <c r="AR10" s="13" t="n"/>
+      <c r="AS10" s="13" t="n"/>
+      <c r="AT10" s="13" t="n"/>
+      <c r="AU10" s="13" t="n"/>
+      <c r="AV10" s="13" t="n"/>
+      <c r="AW10" s="13" t="n"/>
+      <c r="AX10" s="13" t="n"/>
+      <c r="AY10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="D11" s="5">
         <f>IFERROR(C11/$B$5,"")</f>
         <v/>
@@ -2709,15 +3786,6 @@
         <v/>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.3915</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
@@ -2727,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2744,22 +3812,7 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" s="4" t="n">
+      <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
@@ -2780,31 +3833,21 @@
       <c r="AN11" t="n">
         <v>0</v>
       </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:27:56.879192</t>
-        </is>
-      </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756.csv</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-132756\20260929-132756_struct.mat</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261008-161839\20261008-161839.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="D12" s="5">
@@ -2816,10 +3859,10 @@
         <v/>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>20.8231</v>
+        <v>12.6066</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2828,37 +3871,52 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>10</v>
       </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>21</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0.05</v>
+      <c r="AF12" t="b">
+        <v>0</v>
       </c>
       <c r="AH12" s="4" t="n">
         <v>0</v>
@@ -2876,1268 +3934,41 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AR12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10000</v>
+      </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57:42.108067; 2026-09-29 16:16:29.305653; 2026-09-29 16:20:19.853590; 2026-09-29 16:22:43.629419</t>
+          <t>2026-10-08 16:18:49.829389; 2026-10-08 16:19:18.319998; 2026-10-08 16:36:19.558987</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-161628\20260929-161628.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162019\20260929-162019.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-162242\20260929-162242.csv</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261008-161848\20261008-161848.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261008-161917\20261008-161917.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261008-163618\20261008-163618.csv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20260929-155741\20260929-155741_combined_struct.mat</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AY9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
-    <col customWidth="1" max="15" min="15" width="14"/>
-    <col customWidth="1" max="16" min="16" width="14"/>
-    <col customWidth="1" max="17" min="17" width="14"/>
-    <col customWidth="1" max="18" min="18" width="14"/>
-    <col customWidth="1" max="19" min="19" width="14"/>
-    <col customWidth="1" max="20" min="20" width="14"/>
-    <col customWidth="1" max="21" min="21" width="14"/>
-    <col customWidth="1" max="22" min="22" width="14"/>
-    <col customWidth="1" max="23" min="23" width="14"/>
-    <col customWidth="1" max="24" min="24" width="14"/>
-    <col customWidth="1" max="25" min="25" width="14"/>
-    <col customWidth="1" max="26" min="26" width="14"/>
-    <col customWidth="1" max="27" min="27" width="14"/>
-    <col customWidth="1" max="28" min="28" width="14"/>
-    <col customWidth="1" max="29" min="29" width="14"/>
-    <col customWidth="1" max="30" min="30" width="14"/>
-    <col customWidth="1" max="31" min="31" width="14"/>
-    <col customWidth="1" max="32" min="32" width="14"/>
-    <col customWidth="1" max="33" min="33" width="14"/>
-    <col customWidth="1" max="34" min="34" width="14"/>
-    <col customWidth="1" max="35" min="35" width="14"/>
-    <col customWidth="1" max="36" min="36" width="14"/>
-    <col customWidth="1" max="37" min="37" width="14"/>
-    <col customWidth="1" max="38" min="38" width="14"/>
-    <col customWidth="1" max="39" min="39" width="14"/>
-    <col customWidth="1" max="40" min="40" width="14"/>
-    <col customWidth="1" max="41" min="41" width="14"/>
-    <col customWidth="1" max="42" min="42" width="14"/>
-    <col customWidth="1" max="43" min="43" width="14"/>
-    <col customWidth="1" max="44" min="44" width="14"/>
-    <col customWidth="1" max="45" min="45" width="14"/>
-    <col customWidth="1" max="46" min="46" width="14"/>
-    <col customWidth="1" max="47" min="47" width="14"/>
-    <col customWidth="1" max="48" min="48" width="14"/>
-    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
-    <col customWidth="1" max="50" min="50" width="14"/>
-    <col customWidth="1" max="51" min="51" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Animal: test_stage2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Strain</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Baseline weight (g)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Time (HH:MM)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Weight (g)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Weight %</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Weight after task (g)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Weight after task %</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Water given by hand after task</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Trials</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Duration (s)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Reward Amount (uL)</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Total Volume (uL)</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Withheld</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>No-movement</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Wheel Aborts</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>L turns</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>R turns</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>Licks</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold start (deg)</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold end (deg)</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold end (% final)</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>ITI (s)</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>Gain mult (Stage 1)</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>Direction ratio (Stage 2)</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>Simple gates met</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>Response Thresh Start (deg)</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>Response Thresh End (deg)</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>Quiescence Start (s)</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>Quiescence End (s)</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>In-trial Threshold (deg)</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr">
-        <is>
-          <t>Click Attenuated (Stage 3)</t>
-        </is>
-      </c>
-      <c r="AG7" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy (gamma=1.0)</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>Abort Rate</t>
-        </is>
-      </c>
-      <c r="AI7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Quiescence</t>
-        </is>
-      </c>
-      <c r="AJ7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Cue</t>
-        </is>
-      </c>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Delay</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Response</t>
-        </is>
-      </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>Warmup Trials</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>Repeat Trials</t>
-        </is>
-      </c>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>Session Water (uL)</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>Staircase Advanced (Stage 4)</t>
-        </is>
-      </c>
-      <c r="AQ7" s="3" t="inlineStr">
-        <is>
-          <t>Git Commit</t>
-        </is>
-      </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>Target SPL (dB)</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>Left Freq (Hz)</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>Right Freq (Hz)</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Num. Sessions</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>Session started</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>Session data (local path)</t>
-        </is>
-      </c>
-      <c r="AY7" s="3" t="inlineStr">
-        <is>
-          <t>Session struct (local path)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="9" t="n"/>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="9" t="n"/>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="9" t="n"/>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="9" t="n"/>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="9" t="n"/>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="9" t="n"/>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="9" t="n"/>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="9" t="n"/>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="9" t="n"/>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="9" t="n"/>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="9" t="n"/>
-      <c r="AY8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="D9" s="5">
-        <f>IFERROR(C9/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="5">
-        <f>IFERROR(E9/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v>37</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.3952</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>101</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.2424242424242424</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:57:38.677951</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737.csv</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20260918-105737\20260918-105737_struct.mat</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AY11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
-    <col customWidth="1" max="15" min="15" width="14"/>
-    <col customWidth="1" max="16" min="16" width="14"/>
-    <col customWidth="1" max="17" min="17" width="14"/>
-    <col customWidth="1" max="18" min="18" width="14"/>
-    <col customWidth="1" max="19" min="19" width="14"/>
-    <col customWidth="1" max="20" min="20" width="14"/>
-    <col customWidth="1" max="21" min="21" width="14"/>
-    <col customWidth="1" max="22" min="22" width="14"/>
-    <col customWidth="1" max="23" min="23" width="14"/>
-    <col customWidth="1" max="24" min="24" width="14"/>
-    <col customWidth="1" max="25" min="25" width="14"/>
-    <col customWidth="1" max="26" min="26" width="14"/>
-    <col customWidth="1" max="27" min="27" width="14"/>
-    <col customWidth="1" max="28" min="28" width="14"/>
-    <col customWidth="1" max="29" min="29" width="14"/>
-    <col customWidth="1" max="30" min="30" width="14"/>
-    <col customWidth="1" max="31" min="31" width="14"/>
-    <col customWidth="1" max="32" min="32" width="14"/>
-    <col customWidth="1" max="33" min="33" width="14"/>
-    <col customWidth="1" max="34" min="34" width="14"/>
-    <col customWidth="1" max="35" min="35" width="14"/>
-    <col customWidth="1" max="36" min="36" width="14"/>
-    <col customWidth="1" max="37" min="37" width="14"/>
-    <col customWidth="1" max="38" min="38" width="14"/>
-    <col customWidth="1" max="39" min="39" width="14"/>
-    <col customWidth="1" max="40" min="40" width="14"/>
-    <col customWidth="1" max="41" min="41" width="14"/>
-    <col customWidth="1" max="42" min="42" width="14"/>
-    <col customWidth="1" max="43" min="43" width="14"/>
-    <col customWidth="1" max="44" min="44" width="14"/>
-    <col customWidth="1" max="45" min="45" width="14"/>
-    <col customWidth="1" max="46" min="46" width="14"/>
-    <col customWidth="1" max="47" min="47" width="14"/>
-    <col customWidth="1" max="48" min="48" width="14"/>
-    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
-    <col customWidth="1" max="50" min="50" width="14"/>
-    <col customWidth="1" max="51" min="51" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Animal: test_stage3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Strain</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Baseline weight (g)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Time (HH:MM)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Weight (g)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Weight %</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Weight after task (g)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Weight after task %</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Water given by hand after task</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Trials</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Duration (s)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Reward Amount (uL)</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Total Volume (uL)</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Withheld</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>No-movement</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Wheel Aborts</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>L turns</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>R turns</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>Licks</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold start (deg)</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold end (deg)</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Threshold end (% final)</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>ITI (s)</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>Gain mult (Stage 1)</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>Direction ratio (Stage 2)</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>Simple gates met</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>Response Thresh Start (deg)</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>Response Thresh End (deg)</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>Quiescence Start (s)</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>Quiescence End (s)</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>In-trial Threshold (deg)</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr">
-        <is>
-          <t>Click Attenuated (Stage 3)</t>
-        </is>
-      </c>
-      <c r="AG7" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy (gamma=1.0)</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>Abort Rate</t>
-        </is>
-      </c>
-      <c r="AI7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Quiescence</t>
-        </is>
-      </c>
-      <c r="AJ7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Cue</t>
-        </is>
-      </c>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Delay</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="inlineStr">
-        <is>
-          <t>Aborts: Response</t>
-        </is>
-      </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>Warmup Trials</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>Repeat Trials</t>
-        </is>
-      </c>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>Session Water (uL)</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>Staircase Advanced (Stage 4)</t>
-        </is>
-      </c>
-      <c r="AQ7" s="3" t="inlineStr">
-        <is>
-          <t>Git Commit</t>
-        </is>
-      </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>Target SPL (dB)</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>Left Freq (Hz)</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>Right Freq (Hz)</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Num. Sessions</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>Session started</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>Session data (local path)</t>
-        </is>
-      </c>
-      <c r="AY7" s="3" t="inlineStr">
-        <is>
-          <t>Session struct (local path)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Stage 3</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="13" t="n"/>
-      <c r="Y8" s="13" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="13" t="n"/>
-      <c r="AB8" s="13" t="n"/>
-      <c r="AC8" s="13" t="n"/>
-      <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="13" t="n"/>
-      <c r="AF8" s="13" t="n"/>
-      <c r="AG8" s="13" t="n"/>
-      <c r="AH8" s="13" t="n"/>
-      <c r="AI8" s="13" t="n"/>
-      <c r="AJ8" s="13" t="n"/>
-      <c r="AK8" s="13" t="n"/>
-      <c r="AL8" s="13" t="n"/>
-      <c r="AM8" s="13" t="n"/>
-      <c r="AN8" s="13" t="n"/>
-      <c r="AO8" s="13" t="n"/>
-      <c r="AP8" s="13" t="n"/>
-      <c r="AQ8" s="13" t="n"/>
-      <c r="AR8" s="13" t="n"/>
-      <c r="AS8" s="13" t="n"/>
-      <c r="AT8" s="13" t="n"/>
-      <c r="AU8" s="13" t="n"/>
-      <c r="AV8" s="13" t="n"/>
-      <c r="AW8" s="13" t="n"/>
-      <c r="AX8" s="13" t="n"/>
-      <c r="AY8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="D9" s="5">
-        <f>IFERROR(C9/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="5">
-        <f>IFERROR(E9/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2026-09-18 11:07:35.895474</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110734\20260918-110734.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="D10" s="5">
-        <f>IFERROR(C10/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>IFERROR(E10/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>f63385200c72f20c041f38f5d1de44ad97556fe1-dirty</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2026-09-18 11:09:41.608956</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-110940\20260918-110940.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="D11" s="5">
-        <f>IFERROR(C11/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="5">
-        <f>IFERROR(E11/$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="H11" t="n">
-        <v>123</v>
-      </c>
-      <c r="I11" t="n">
-        <v>35.70160000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16</v>
-      </c>
-      <c r="O11" t="n">
-        <v>7</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17</v>
-      </c>
-      <c r="R11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>62</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>35</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>35</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="4" t="n">
-        <v>0.06504065040650407</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AR11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2026-09-18 15:36:43.713222; 2026-09-18 15:37:53.276990; 2026-09-18 16:09:07.462610; 2026-09-18 16:12:06.495495; 2026-09-18 16:38:36.208995; 2026-09-18 17:04:41.641105; 2026-09-18 17:10:06.487381</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153752\20260918-153752.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-160906\20260918-160906.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-161205\20260918-161205.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-163835\20260918-163835.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-170440\20260918-170440.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-171005\20260918-171005.csv</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20260918-153642\20260918-153642_combined_struct.mat</t>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261008-161848\20261008-161848_combined_struct.mat</t>
         </is>
       </c>
     </row>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -11,6 +11,7 @@
     <sheet name="testTask" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="test2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="test3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="test1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3975,4 +3976,979 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" max="1" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="50" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Animal: test1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Time (HH:MM)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Weight (g)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weight %</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task (g)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Weight after task %</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Water given by hand after task</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Reward Amount (uL)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Total Volume (uL)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Withheld</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>No-movement</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wheel Aborts</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>L turns</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R turns</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Licks</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold start (deg)</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (deg)</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Threshold end (% final)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ITI (s)</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Gain mult (Stage 1)</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Direction ratio (Stage 2)</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Simple gates met</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh Start (deg)</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Response Thresh End (deg)</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence Start (s)</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Quiescence End (s)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>In-trial Threshold (deg)</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Click Attenuated (Stage 4)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy (gamma=1.0)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>Abort Rate</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Quiescence</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Cue</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Delay</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aborts: Response</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Warmup Trials</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Trials</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>Session Water (uL)</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>Staircase Advanced (Stage 5)</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>Git Commit</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Target SPL (dB)</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>Left Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>Right Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Num. Sessions</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>Session started</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Session data (local path)</t>
+        </is>
+      </c>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>Session struct (local path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="7" t="n"/>
+      <c r="AE8" s="7" t="n"/>
+      <c r="AF8" s="7" t="n"/>
+      <c r="AG8" s="7" t="n"/>
+      <c r="AH8" s="7" t="n"/>
+      <c r="AI8" s="7" t="n"/>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="7" t="n"/>
+      <c r="AS8" s="7" t="n"/>
+      <c r="AT8" s="7" t="n"/>
+      <c r="AU8" s="7" t="n"/>
+      <c r="AV8" s="7" t="n"/>
+      <c r="AW8" s="7" t="n"/>
+      <c r="AX8" s="7" t="n"/>
+      <c r="AY8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="D9" s="5">
+        <f>IFERROR(C9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(E9/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.8629</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>70</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:42:47.094626</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261013-114246\20261013-114246.csv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261013-114246\20261013-114246_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D10" s="5">
+        <f>IFERROR(C10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>IFERROR(E10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45:19.843221</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261013-114519\20261013-114519.csv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261013-114519\20261013-114519_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="9" t="n"/>
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="9" t="n"/>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="9" t="n"/>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="9" t="n"/>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="9" t="n"/>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="9" t="n"/>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="9" t="n"/>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="9" t="n"/>
+      <c r="AY11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="D12" s="5">
+        <f>IFERROR(C12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>IFERROR(E12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10.4954</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>98</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>24</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:44:01.488979</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20261013-114400\20261013-114400.csv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20261013-114400\20261013-114400_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="13" t="n"/>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="13" t="n"/>
+      <c r="Y13" s="13" t="n"/>
+      <c r="Z13" s="13" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="13" t="n"/>
+      <c r="AC13" s="13" t="n"/>
+      <c r="AD13" s="13" t="n"/>
+      <c r="AE13" s="13" t="n"/>
+      <c r="AF13" s="13" t="n"/>
+      <c r="AG13" s="13" t="n"/>
+      <c r="AH13" s="13" t="n"/>
+      <c r="AI13" s="13" t="n"/>
+      <c r="AJ13" s="13" t="n"/>
+      <c r="AK13" s="13" t="n"/>
+      <c r="AL13" s="13" t="n"/>
+      <c r="AM13" s="13" t="n"/>
+      <c r="AN13" s="13" t="n"/>
+      <c r="AO13" s="13" t="n"/>
+      <c r="AP13" s="13" t="n"/>
+      <c r="AQ13" s="13" t="n"/>
+      <c r="AR13" s="13" t="n"/>
+      <c r="AS13" s="13" t="n"/>
+      <c r="AT13" s="13" t="n"/>
+      <c r="AU13" s="13" t="n"/>
+      <c r="AV13" s="13" t="n"/>
+      <c r="AW13" s="13" t="n"/>
+      <c r="AX13" s="13" t="n"/>
+      <c r="AY13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(C14/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>IFERROR(E14/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>35</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.895900000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>105</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>16</v>
+      </c>
+      <c r="S14" t="n">
+        <v>18</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AR14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45:30.059502</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261013-114528\20261013-114528.csv</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage3\setups\Stage3\sessions\20261013-114528\20261013-114528_struct.mat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
 </file>
--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -2,30 +2,45 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="9375" windowWidth="23160" xWindow="0" yWindow="0"/>
   </bookViews>
   <sheets>
     <sheet name="UM001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="test_stage1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt formatCode="0.0%" numFmtId="164"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,7 +54,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,22 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,30 +82,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -461,63 +467,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col hidden="1" width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
+    <col customWidth="1" max="48" min="1" width="14"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="14"/>
+    <col customWidth="1" max="12" min="12" width="14"/>
+    <col customWidth="1" max="13" min="13" width="14"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="14"/>
+    <col customWidth="1" max="16" min="16" width="14"/>
+    <col customWidth="1" max="17" min="17" width="14"/>
+    <col customWidth="1" max="18" min="18" width="14"/>
+    <col customWidth="1" max="19" min="19" width="14"/>
+    <col customWidth="1" max="20" min="20" width="14"/>
+    <col customWidth="1" max="21" min="21" width="14"/>
+    <col customWidth="1" max="22" min="22" width="14"/>
+    <col customWidth="1" max="23" min="23" width="14"/>
+    <col customWidth="1" max="24" min="24" width="14"/>
+    <col customWidth="1" max="25" min="25" width="14"/>
+    <col customWidth="1" max="26" min="26" width="14"/>
+    <col customWidth="1" max="27" min="27" width="14"/>
+    <col customWidth="1" max="28" min="28" width="14"/>
+    <col customWidth="1" max="29" min="29" width="14"/>
+    <col customWidth="1" max="30" min="30" width="14"/>
+    <col customWidth="1" max="31" min="31" width="14"/>
+    <col customWidth="1" max="32" min="32" width="14"/>
+    <col customWidth="1" max="33" min="33" width="14"/>
+    <col customWidth="1" max="34" min="34" width="14"/>
+    <col customWidth="1" max="35" min="35" width="14"/>
+    <col customWidth="1" max="36" min="36" width="14"/>
+    <col customWidth="1" max="37" min="37" width="14"/>
+    <col customWidth="1" max="38" min="38" width="14"/>
+    <col customWidth="1" max="39" min="39" width="14"/>
+    <col customWidth="1" max="40" min="40" width="14"/>
+    <col customWidth="1" max="41" min="41" width="14"/>
+    <col customWidth="1" max="42" min="42" width="14"/>
+    <col customWidth="1" max="43" min="43" width="14"/>
+    <col customWidth="1" max="44" min="44" width="14"/>
+    <col customWidth="1" max="45" min="45" width="14"/>
+    <col customWidth="1" max="46" min="46" width="14"/>
+    <col customWidth="1" max="47" min="47" width="14"/>
+    <col customWidth="1" max="48" min="48" width="14"/>
+    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
+    <col customWidth="1" max="51" min="50" width="14"/>
+    <col customWidth="1" max="51" min="51" width="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row customHeight="1" ht="15.75" r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Animal: UM001</t>
@@ -572,319 +578,319 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row customHeight="1" ht="45" r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Time (HH:MM)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Weight (g)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Weight after task (g)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Weight after task %</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Water given by hand after task</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Trials</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Duration (s)</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Reward Amount (uL)</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Total Volume (uL)</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>Aborts</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Withheld</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>No-movement</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>Wheel Aborts</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>L turns</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr">
         <is>
           <t>R turns</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Licks</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="10" t="inlineStr">
         <is>
           <t>Threshold start (deg)</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="10" t="inlineStr">
         <is>
           <t>Threshold end (deg)</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="10" t="inlineStr">
         <is>
           <t>Threshold end (% final)</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>ITI (s)</t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="10" t="inlineStr">
         <is>
           <t>Gain mult (Stage 1)</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="Y7" s="10" t="inlineStr">
         <is>
           <t>Direction ratio (Stage 2)</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="10" t="inlineStr">
         <is>
           <t>Simple gates met</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="inlineStr">
+      <c r="AA7" s="10" t="inlineStr">
         <is>
           <t>Response Thresh Start (deg)</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="AB7" s="10" t="inlineStr">
         <is>
           <t>Response Thresh End (deg)</t>
         </is>
       </c>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AC7" s="10" t="inlineStr">
         <is>
           <t>Quiescence Start (s)</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="10" t="inlineStr">
         <is>
           <t>Quiescence End (s)</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE7" s="10" t="inlineStr">
         <is>
           <t>In-trial Threshold (deg)</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="inlineStr">
+      <c r="AF7" s="10" t="inlineStr">
         <is>
           <t>Click Attenuated (Stage 4)</t>
         </is>
       </c>
-      <c r="AG7" s="3" t="inlineStr">
+      <c r="AG7" s="10" t="inlineStr">
         <is>
           <t>Accuracy (gamma=1.0)</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
+      <c r="AH7" s="10" t="inlineStr">
         <is>
           <t>Abort Rate</t>
         </is>
       </c>
-      <c r="AI7" s="3" t="inlineStr">
+      <c r="AI7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Quiescence</t>
         </is>
       </c>
-      <c r="AJ7" s="3" t="inlineStr">
+      <c r="AJ7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Cue</t>
         </is>
       </c>
-      <c r="AK7" s="3" t="inlineStr">
+      <c r="AK7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Delay</t>
         </is>
       </c>
-      <c r="AL7" s="3" t="inlineStr">
+      <c r="AL7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Response</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
+      <c r="AM7" s="10" t="inlineStr">
         <is>
           <t>Warmup Trials</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
+      <c r="AN7" s="10" t="inlineStr">
         <is>
           <t>Repeat Trials</t>
         </is>
       </c>
-      <c r="AO7" s="3" t="inlineStr">
+      <c r="AO7" s="10" t="inlineStr">
         <is>
           <t>Session Water (uL)</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
+      <c r="AP7" s="10" t="inlineStr">
         <is>
           <t>Staircase Advanced (Stage 5)</t>
         </is>
       </c>
-      <c r="AQ7" s="3" t="inlineStr">
+      <c r="AQ7" s="10" t="inlineStr">
         <is>
           <t>Git Commit</t>
         </is>
       </c>
-      <c r="AR7" s="3" t="inlineStr">
+      <c r="AR7" s="10" t="inlineStr">
         <is>
           <t>Target SPL (dB)</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AS7" s="10" t="inlineStr">
         <is>
           <t>Left Freq (Hz)</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
+      <c r="AT7" s="10" t="inlineStr">
         <is>
           <t>Right Freq (Hz)</t>
         </is>
       </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AU7" s="10" t="inlineStr">
         <is>
           <t>Num. Sessions</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
+      <c r="AV7" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AW7" s="10" t="inlineStr">
         <is>
           <t>Session started</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr">
+      <c r="AX7" s="10" t="inlineStr">
         <is>
           <t>Session data (local path)</t>
         </is>
       </c>
-      <c r="AY7" s="3" t="inlineStr">
+      <c r="AY7" s="10" t="inlineStr">
         <is>
           <t>Session struct (local path)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Stage 1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="7" t="n"/>
-      <c r="AB8" s="7" t="n"/>
-      <c r="AC8" s="7" t="n"/>
-      <c r="AD8" s="7" t="n"/>
-      <c r="AE8" s="7" t="n"/>
-      <c r="AF8" s="7" t="n"/>
-      <c r="AG8" s="7" t="n"/>
-      <c r="AH8" s="7" t="n"/>
-      <c r="AI8" s="7" t="n"/>
-      <c r="AJ8" s="7" t="n"/>
-      <c r="AK8" s="7" t="n"/>
-      <c r="AL8" s="7" t="n"/>
-      <c r="AM8" s="7" t="n"/>
-      <c r="AN8" s="7" t="n"/>
-      <c r="AO8" s="7" t="n"/>
-      <c r="AP8" s="7" t="n"/>
-      <c r="AQ8" s="7" t="n"/>
-      <c r="AR8" s="7" t="n"/>
-      <c r="AS8" s="7" t="n"/>
-      <c r="AT8" s="7" t="n"/>
-      <c r="AU8" s="7" t="n"/>
-      <c r="AV8" s="7" t="n"/>
-      <c r="AW8" s="7" t="n"/>
-      <c r="AX8" s="7" t="n"/>
-      <c r="AY8" s="7" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="12" t="n"/>
+      <c r="S8" s="12" t="n"/>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="12" t="n"/>
+      <c r="Y8" s="12" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="12" t="n"/>
+      <c r="AB8" s="12" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="12" t="n"/>
+      <c r="AE8" s="12" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="12" t="n"/>
+      <c r="AH8" s="12" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="12" t="n"/>
+      <c r="AK8" s="12" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="12" t="n"/>
+      <c r="AN8" s="12" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="12" t="n"/>
+      <c r="AQ8" s="12" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="12" t="n"/>
+      <c r="AT8" s="12" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="12" t="n"/>
+      <c r="AW8" s="12" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -942,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="R9" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="S9" t="n">
         <v>160</v>
@@ -1007,7 +1013,404 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5">
+        <f>IFERROR(C10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F10" s="5">
+        <f>IFERROR(E10/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>62</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.4986</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>460</v>
+      </c>
+      <c r="L10" t="n">
+        <v>387</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>30</v>
+      </c>
+      <c r="S10" t="n">
+        <v>527</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:57:06.324806</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-135705\20261022-135705.csv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-135705\20261022-135705_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <f>IFERROR(C11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F11" s="5">
+        <f>IFERROR(E11/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>191</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.4999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L11" t="n">
+        <v>366</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>41</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>91</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1909</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:02:22.920559</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-140221\20261022-140221.csv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-140221\20261022-140221_struct.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D12" s="5">
+        <f>IFERROR(C12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F12" s="5">
+        <f>IFERROR(E12/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>221</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.7722</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L12" t="n">
+        <v>103</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>111</v>
+      </c>
+      <c r="R12" t="n">
+        <v>104</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2131</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:28:44.823299</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261027-102843\20261027-102843.csv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261027-102843\20261027-102843_struct.mat</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Animal: test_stage1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Baseline weight (g)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="48" min="1" width="14"/>
@@ -518,9 +518,10 @@
     <col customWidth="1" max="46" min="46" width="14"/>
     <col customWidth="1" max="47" min="47" width="14"/>
     <col customWidth="1" max="48" min="48" width="14"/>
-    <col customWidth="1" hidden="1" max="49" min="49" width="14"/>
-    <col customWidth="1" max="51" min="50" width="14"/>
+    <col customWidth="1" max="49" min="49" width="14"/>
+    <col customWidth="1" hidden="1" max="51" min="50" width="14"/>
     <col customWidth="1" max="51" min="51" width="14"/>
+    <col customWidth="1" max="52" min="52" width="14"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="15.75" r="1">
@@ -631,205 +632,210 @@
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Total Volume (uL)</t>
+          <t>Water Consumed (uL)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
+          <t>Water Delivered (uL)</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
           <t>Aborts</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Withheld</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>No-movement</t>
         </is>
       </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>Wheel Aborts</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr">
         <is>
           <t>L turns</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>R turns</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="T7" s="10" t="inlineStr">
         <is>
           <t>Licks</t>
         </is>
       </c>
-      <c r="T7" s="10" t="inlineStr">
+      <c r="U7" s="10" t="inlineStr">
         <is>
           <t>Threshold start (deg)</t>
         </is>
       </c>
-      <c r="U7" s="10" t="inlineStr">
+      <c r="V7" s="10" t="inlineStr">
         <is>
           <t>Threshold end (deg)</t>
         </is>
       </c>
-      <c r="V7" s="10" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>Threshold end (% final)</t>
         </is>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="X7" s="10" t="inlineStr">
         <is>
           <t>ITI (s)</t>
         </is>
       </c>
-      <c r="X7" s="10" t="inlineStr">
+      <c r="Y7" s="10" t="inlineStr">
         <is>
           <t>Gain mult (Stage 1)</t>
         </is>
       </c>
-      <c r="Y7" s="10" t="inlineStr">
+      <c r="Z7" s="10" t="inlineStr">
         <is>
           <t>Direction ratio (Stage 2)</t>
         </is>
       </c>
-      <c r="Z7" s="10" t="inlineStr">
+      <c r="AA7" s="10" t="inlineStr">
         <is>
           <t>Simple gates met</t>
         </is>
       </c>
-      <c r="AA7" s="10" t="inlineStr">
+      <c r="AB7" s="10" t="inlineStr">
         <is>
           <t>Response Thresh Start (deg)</t>
         </is>
       </c>
-      <c r="AB7" s="10" t="inlineStr">
+      <c r="AC7" s="10" t="inlineStr">
         <is>
           <t>Response Thresh End (deg)</t>
         </is>
       </c>
-      <c r="AC7" s="10" t="inlineStr">
+      <c r="AD7" s="10" t="inlineStr">
         <is>
           <t>Quiescence Start (s)</t>
         </is>
       </c>
-      <c r="AD7" s="10" t="inlineStr">
+      <c r="AE7" s="10" t="inlineStr">
         <is>
           <t>Quiescence End (s)</t>
         </is>
       </c>
-      <c r="AE7" s="10" t="inlineStr">
+      <c r="AF7" s="10" t="inlineStr">
         <is>
           <t>In-trial Threshold (deg)</t>
         </is>
       </c>
-      <c r="AF7" s="10" t="inlineStr">
+      <c r="AG7" s="10" t="inlineStr">
         <is>
           <t>Click Attenuated (Stage 4)</t>
         </is>
       </c>
-      <c r="AG7" s="10" t="inlineStr">
+      <c r="AH7" s="10" t="inlineStr">
         <is>
           <t>Accuracy (gamma=1.0)</t>
         </is>
       </c>
-      <c r="AH7" s="10" t="inlineStr">
+      <c r="AI7" s="10" t="inlineStr">
         <is>
           <t>Abort Rate</t>
         </is>
       </c>
-      <c r="AI7" s="10" t="inlineStr">
+      <c r="AJ7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Quiescence</t>
         </is>
       </c>
-      <c r="AJ7" s="10" t="inlineStr">
+      <c r="AK7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Cue</t>
         </is>
       </c>
-      <c r="AK7" s="10" t="inlineStr">
+      <c r="AL7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Delay</t>
         </is>
       </c>
-      <c r="AL7" s="10" t="inlineStr">
+      <c r="AM7" s="10" t="inlineStr">
         <is>
           <t>Aborts: Response</t>
         </is>
       </c>
-      <c r="AM7" s="10" t="inlineStr">
+      <c r="AN7" s="10" t="inlineStr">
         <is>
           <t>Warmup Trials</t>
         </is>
       </c>
-      <c r="AN7" s="10" t="inlineStr">
+      <c r="AO7" s="10" t="inlineStr">
         <is>
           <t>Repeat Trials</t>
         </is>
       </c>
-      <c r="AO7" s="10" t="inlineStr">
+      <c r="AP7" s="10" t="inlineStr">
         <is>
           <t>Session Water (uL)</t>
         </is>
       </c>
-      <c r="AP7" s="10" t="inlineStr">
+      <c r="AQ7" s="10" t="inlineStr">
         <is>
           <t>Staircase Advanced (Stage 5)</t>
         </is>
       </c>
-      <c r="AQ7" s="10" t="inlineStr">
+      <c r="AR7" s="10" t="inlineStr">
         <is>
           <t>Git Commit</t>
         </is>
       </c>
-      <c r="AR7" s="10" t="inlineStr">
+      <c r="AS7" s="10" t="inlineStr">
         <is>
           <t>Target SPL (dB)</t>
         </is>
       </c>
-      <c r="AS7" s="10" t="inlineStr">
+      <c r="AT7" s="10" t="inlineStr">
         <is>
           <t>Left Freq (Hz)</t>
         </is>
       </c>
-      <c r="AT7" s="10" t="inlineStr">
+      <c r="AU7" s="10" t="inlineStr">
         <is>
           <t>Right Freq (Hz)</t>
         </is>
       </c>
-      <c r="AU7" s="10" t="inlineStr">
+      <c r="AV7" s="10" t="inlineStr">
         <is>
           <t>Num. Sessions</t>
         </is>
       </c>
-      <c r="AV7" s="10" t="inlineStr">
+      <c r="AW7" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AW7" s="10" t="inlineStr">
+      <c r="AX7" s="10" t="inlineStr">
         <is>
           <t>Session started</t>
         </is>
       </c>
-      <c r="AX7" s="10" t="inlineStr">
+      <c r="AY7" s="10" t="inlineStr">
         <is>
           <t>Session data (local path)</t>
         </is>
       </c>
-      <c r="AY7" s="10" t="inlineStr">
+      <c r="AZ7" s="10" t="inlineStr">
         <is>
           <t>Session struct (local path)</t>
         </is>
@@ -891,6 +897,7 @@
       <c r="AW8" s="12" t="n"/>
       <c r="AX8" s="12" t="n"/>
       <c r="AY8" s="12" t="n"/>
+      <c r="AZ8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -930,51 +937,51 @@
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>245</v>
+        <v>777</v>
       </c>
       <c r="L9" t="n">
+        <v>973</v>
+      </c>
+      <c r="M9" t="n">
         <v>222</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>75</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>69</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>70</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>160</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
       </c>
       <c r="U9" t="n">
         <v>3.5</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="V9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.5</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>3</v>
       </c>
-      <c r="AH9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
+      <c r="AI9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
@@ -992,22 +999,25 @@
       <c r="AN9" t="n">
         <v>0</v>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="inlineStr">
         <is>
           <t>the stopping has helped, initially was bad but once paws hit the wheel it was good</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>2026-10-21 15:22:36.631959</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261021-152235\20261021-152235.csv</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261021-152235\20261021-152235_struct.mat</t>
         </is>
@@ -1051,51 +1061,51 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>460</v>
+        <v>520</v>
       </c>
       <c r="L10" t="n">
+        <v>520</v>
+      </c>
+      <c r="M10" t="n">
         <v>387</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>10</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>22</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>30</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>527</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.2</v>
       </c>
       <c r="U10" t="n">
         <v>4.2</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="V10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.4999999999999999</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>2.9</v>
       </c>
-      <c r="AH10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AI10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
@@ -1113,17 +1123,20 @@
       <c r="AN10" t="n">
         <v>0</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="inlineStr">
         <is>
           <t>2026-10-22 13:57:06.324806</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-135705\20261022-135705.csv</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-135705\20261022-135705_struct.mat</t>
         </is>
@@ -1167,51 +1180,51 @@
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>1170</v>
+        <v>1500</v>
       </c>
       <c r="L11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M11" t="n">
         <v>366</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>41</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>59</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>91</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1909</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.2</v>
       </c>
       <c r="U11" t="n">
         <v>4.2</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="V11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W11" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.5</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>2.9</v>
       </c>
-      <c r="AH11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
+      <c r="AI11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
@@ -1229,17 +1242,20 @@
       <c r="AN11" t="n">
         <v>0</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="inlineStr">
         <is>
           <t>2026-10-22 14:02:22.920559</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-140221\20261022-140221.csv</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261022-140221\20261022-140221_struct.mat</t>
         </is>
@@ -1283,51 +1299,51 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>1470</v>
+        <v>1505</v>
       </c>
       <c r="L12" t="n">
+        <v>1505</v>
+      </c>
+      <c r="M12" t="n">
         <v>103</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>111</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>104</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2131</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.9</v>
       </c>
       <c r="U12" t="n">
         <v>4.9</v>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="V12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W12" s="4" t="n">
         <v>0.14</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.5</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>2.8</v>
       </c>
-      <c r="AH12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
+      <c r="AI12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
@@ -1345,17 +1361,20 @@
       <c r="AN12" t="n">
         <v>0</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>2026-10-27 10:28:44.823299</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261027-102843\20261027-102843.csv</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261027-102843\20261027-102843_struct.mat</t>
         </is>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -964,7 +964,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U9" t="n">
         <v>3.5</v>
@@ -1088,7 +1088,7 @@
         <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>527</v>
+        <v>247</v>
       </c>
       <c r="U10" t="n">
         <v>4.2</v>
@@ -1207,7 +1207,7 @@
         <v>91</v>
       </c>
       <c r="T11" t="n">
-        <v>1909</v>
+        <v>600</v>
       </c>
       <c r="U11" t="n">
         <v>4.2</v>
@@ -1326,7 +1326,7 @@
         <v>104</v>
       </c>
       <c r="T12" t="n">
-        <v>2131</v>
+        <v>1757</v>
       </c>
       <c r="U12" t="n">
         <v>4.9</v>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="48" min="1" width="14"/>
@@ -1380,6 +1380,128 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="5">
+        <f>IFERROR(C13/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F13" s="5">
+        <f>IFERROR(E13/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>303</v>
+      </c>
+      <c r="I13" t="n">
+        <v>16.4147</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2121</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2121</v>
+      </c>
+      <c r="M13" t="n">
+        <v>114</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>158</v>
+      </c>
+      <c r="S13" t="n">
+        <v>145</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:54:47.097793; 2026-10-28 15:00:58.356534</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261028-145445\20261028-145445.csv; C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261028-150056\20261028-150056.csv</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261028-145445\20261028-145445_combined_struct.mat</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -931,7 +931,7 @@
         <v>214</v>
       </c>
       <c r="I9" t="n">
-        <v>10.4995</v>
+        <v>1269.200002</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
@@ -1055,7 +1055,7 @@
         <v>62</v>
       </c>
       <c r="I10" t="n">
-        <v>10.4986</v>
+        <v>225.758103</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
         <v>191</v>
       </c>
       <c r="I11" t="n">
-        <v>10.4999</v>
+        <v>927.9607020000001</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>221</v>
       </c>
       <c r="I12" t="n">
-        <v>11.7722</v>
+        <v>573.3331030000001</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>303</v>
       </c>
       <c r="I13" t="n">
-        <v>16.4147</v>
+        <v>454.989606</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Duration (s)</t>
+          <t>Duration (min)</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
@@ -931,7 +931,7 @@
         <v>214</v>
       </c>
       <c r="I9" t="n">
-        <v>1269.200002</v>
+        <v>21.2</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
@@ -1055,7 +1055,7 @@
         <v>62</v>
       </c>
       <c r="I10" t="n">
-        <v>225.758103</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
         <v>191</v>
       </c>
       <c r="I11" t="n">
-        <v>927.9607020000001</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>221</v>
       </c>
       <c r="I12" t="n">
-        <v>573.3331030000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>303</v>
       </c>
       <c r="I13" t="n">
-        <v>454.989606</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="48" min="1" width="14"/>
@@ -1502,6 +1502,116 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(C14/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>IFERROR(E14/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v>215</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1505</v>
+      </c>
+      <c r="M14" t="n">
+        <v>104</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>112</v>
+      </c>
+      <c r="S14" t="n">
+        <v>103</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2056</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6.999999999999999</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.999999999999999</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:42:34.495925</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261029-144232\20261029-144232.csv</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage1\setups\Stage1\sessions\20261029-144232\20261029-144232_struct.mat</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -1513,13 +1513,22 @@
           <t>14:42</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>25.1</v>
+      </c>
       <c r="D14" s="5">
         <f>IFERROR(C14/$B$5,"")</f>
         <v/>
       </c>
+      <c r="E14" t="n">
+        <v>26</v>
+      </c>
       <c r="F14" s="5">
         <f>IFERROR(E14/$B$5,"")</f>
         <v/>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>215</v>

--- a/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
+++ b/_projects/AuditoryEvidenceAccum/records/training_log.xlsx
@@ -54,7 +54,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +107,8 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle builtinId="0" name="Normal" xfId="0"/>
@@ -467,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="48" min="1" width="14"/>
@@ -1621,6 +1628,192 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="14" t="n"/>
+      <c r="P15" s="14" t="n"/>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="n"/>
+      <c r="T15" s="14" t="n"/>
+      <c r="U15" s="14" t="n"/>
+      <c r="V15" s="14" t="n"/>
+      <c r="W15" s="14" t="n"/>
+      <c r="X15" s="14" t="n"/>
+      <c r="Y15" s="14" t="n"/>
+      <c r="Z15" s="14" t="n"/>
+      <c r="AA15" s="14" t="n"/>
+      <c r="AB15" s="14" t="n"/>
+      <c r="AC15" s="14" t="n"/>
+      <c r="AD15" s="14" t="n"/>
+      <c r="AE15" s="14" t="n"/>
+      <c r="AF15" s="14" t="n"/>
+      <c r="AG15" s="14" t="n"/>
+      <c r="AH15" s="14" t="n"/>
+      <c r="AI15" s="14" t="n"/>
+      <c r="AJ15" s="14" t="n"/>
+      <c r="AK15" s="14" t="n"/>
+      <c r="AL15" s="14" t="n"/>
+      <c r="AM15" s="14" t="n"/>
+      <c r="AN15" s="14" t="n"/>
+      <c r="AO15" s="14" t="n"/>
+      <c r="AP15" s="14" t="n"/>
+      <c r="AQ15" s="14" t="n"/>
+      <c r="AR15" s="14" t="n"/>
+      <c r="AS15" s="14" t="n"/>
+      <c r="AT15" s="14" t="n"/>
+      <c r="AU15" s="14" t="n"/>
+      <c r="AV15" s="14" t="n"/>
+      <c r="AW15" s="14" t="n"/>
+      <c r="AX15" s="14" t="n"/>
+      <c r="AY15" s="14" t="n"/>
+      <c r="AZ15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D16" s="5">
+        <f>IFERROR(C16/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F16" s="5">
+        <f>IFERROR(E16/$B$5,"")</f>
+        <v/>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>250</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1491</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1491</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17</v>
+      </c>
+      <c r="N16" t="n">
+        <v>22</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>124</v>
+      </c>
+      <c r="S16" t="n">
+        <v>111</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2805</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:21:32.299714</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20261030-142131\20261030-142131.csv</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>C:\Ugurcan\Experimental-Tasks\_projects\AuditoryEvidenceAccum\experiments\Stage2\setups\Stage2\sessions\20261030-142131\20261030-142131_struct.mat</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
